--- a/Publications_By_Faculty_2025-2026.xlsx
+++ b/Publications_By_Faculty_2025-2026.xlsx
@@ -239,17 +239,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-3-031-78937-3_20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-3-031-78937-3_20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Verified (High)</t>
         </is>
       </c>
     </row>
@@ -296,17 +296,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-3-031-78937-3_19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-3-031-78937-3_19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Verified (High)</t>
         </is>
       </c>
     </row>
@@ -353,17 +353,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-3-031-78943-4_17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-3-031-78943-4_17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Verified (High)</t>
         </is>
       </c>
     </row>
@@ -410,17 +410,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-3-031-78943-4_14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-3-031-78943-4_14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Verified (High)</t>
         </is>
       </c>
     </row>
@@ -467,17 +467,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-3-031-78943-4_25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-3-031-78943-4_25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Verified (High)</t>
         </is>
       </c>
     </row>

--- a/Publications_By_Faculty_2025-2026.xlsx
+++ b/Publications_By_Faculty_2025-2026.xlsx
@@ -135,7 +135,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -182,17 +182,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.52209/2706-977X_2025_2_58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.52209/2706-977X_2025_2_58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -239,17 +239,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1007/978-3-031-78937-3_20</t>
+          <t/>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.1007/978-3-031-78937-3_20</t>
+          <t/>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -306,7 +306,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -363,7 +363,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -420,7 +420,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -581,17 +581,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICCCCM61016.2024.11039956</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICCCCM61016.2024.11039956</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -638,17 +638,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-981-96-3253-4_1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-981-96-3253-4_1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.3233/MGC-230113</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.3233/MGC-230113</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://oam-rc.inoe.ro/articles/photonic-crystal-based-finer-surface-plasmonic-sensor-for-detecting-cancer/</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Link only (no DOI)</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/s42044-025-00295-z</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/s42044-025-00295-z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1037,17 +1037,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.13005/bpj/3165</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.13005/bpj/3165</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269058</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269058</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1151,17 +1151,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269231</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269231</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269150</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269247</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269247</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269232</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269232</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1379,17 +1379,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269404</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269404</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1436,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269405</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269405</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1493,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269060</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269060</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0269056</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0269056</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://www.proceedings.com/content/081/081139webtoc.pdf</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Link only (no DOI)</t>
         </is>
       </c>
     </row>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICDSIS65355.2025.11070957</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICDSIS65355.2025.11070957</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1721,17 +1721,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/s40009-025-01769-1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/s40009-025-01769-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1778,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.23919/INDIACom66777.2025.11115857</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.23919/INDIACom66777.2025.11115857</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/EAIC66483.2025.11101351</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/EAIC66483.2025.11101351</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://www.proceedings.com/content/082/082000webtoc.pdf</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Link only (no DOI)</t>
         </is>
       </c>
     </row>
@@ -1949,17 +1949,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/EAIC66483.2025.11101551</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/EAIC66483.2025.11101551</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2177,17 +2177,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/s40009-025-01850-9</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/s40009-025-01850-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2234,17 +2234,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1016/j.nxmate.2025.101240</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1016/j.nxmate.2025.101240</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICCMC65190.2025.11140716</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICCMC65190.2025.11140716</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2462,17 +2462,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/s40009-025-01846-5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/s40009-025-01846-5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://verjournal.com/index.php/ver/article/view/719</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">Link only (no DOI)</t>
         </is>
       </c>
     </row>
@@ -2576,17 +2576,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICIMIA67127.2025.11200871</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICIMIA67127.2025.11200871</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICIMIA67127.2025.11200644</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICIMIA67127.2025.11200644</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2804,17 +2804,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/s11277-025-11870-9</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/s11277-025-11870-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.5269/bspm.78062</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.5269/bspm.78062</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -2975,17 +2975,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/INCSST64791.2025.11210424</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/INCSST64791.2025.11210424</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3032,17 +3032,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/INCSST64791.2025.11210298</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/INCSST64791.2025.11210298</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/INCSST64791.2025.11210368</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/INCSST64791.2025.11210368</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3146,17 +3146,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICCDS64403.2025.11209431</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICCDS64403.2025.11209431</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3203,17 +3203,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-981-96-9203-3_15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-981-96-9203-3_15</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IC2E365635.2025.11167331</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IC2E365635.2025.11167331</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3317,17 +3317,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1201/9781779643346-16</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1201/9781779643346-16</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3374,17 +3374,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1201/9781779643346-12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1201/9781779643346-12</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3431,17 +3431,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1201/9781779643346-9</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1201/9781779643346-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3488,17 +3488,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1002/9781394411283.ch10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1002/9781394411283.ch10</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3602,17 +3602,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1016/j.chemphys.2025.113071</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1016/j.chemphys.2025.113071</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3659,17 +3659,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-3-032-04418-1_7</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-3-032-04418-1_7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3773,17 +3773,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1088/1742-6596/3154/1/012012</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1088/1742-6596/3154/1/012012</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3830,17 +3830,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.5269/bspm.68304</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.5269/bspm.68304</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3887,17 +3887,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICCCNP63914.2025.11233253</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICCCNP63914.2025.11233253</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -4058,17 +4058,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICCAMS65118.2025.11234544</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICCAMS65118.2025.11234544</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4115,17 +4115,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1016/j.egyr.2026.109034</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1016/j.egyr.2026.109034</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4172,17 +4172,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1108/wje-06-2025-0439</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1108/wje-06-2025-0439</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4457,17 +4457,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.26782/jmcms.2026.01.00002</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.26782/jmcms.2026.01.00002</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4571,17 +4571,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-981-95-3389-3_28</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-981-95-3389-3_28</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -4685,17 +4685,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CISES66934.2025.11265594</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CISES66934.2025.11265594</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -4799,17 +4799,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CISES66934.2025.11265636</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CISES66934.2025.11265636</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4856,17 +4856,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CISES66934.2025.11265013</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CISES66934.2025.11265013</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4913,17 +4913,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CISES66934.2025.11265133</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CISES66934.2025.11265133</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -4970,17 +4970,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CISES66934.2025.11265050</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CISES66934.2025.11265050</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5027,17 +5027,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CISES66934.2025.11265067</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CISES66934.2025.11265067</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5084,17 +5084,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-981-95-6063-9_31</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-981-95-6063-9_31</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5141,17 +5141,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1049/itr2.70167</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1049/itr2.70167</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/978-981-95-6063-9_7</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/978-981-95-6063-9_7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5255,17 +5255,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0330831</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0330831</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5312,17 +5312,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0330769</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0330769</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.35377/saucis.1754132</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.35377/saucis.1754132</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.5269/bspm.81200</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.5269/bspm.81200</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5483,17 +5483,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1063/5.0330557</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1063/5.0330557</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5597,17 +5597,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/s40009-026-02108-8</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/s40009-026-02108-8</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5654,17 +5654,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1007/s11831-026-10565-z</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1007/s11831-026-10565-z</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5768,17 +5768,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.5269/bspm.81134</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.5269/bspm.81134</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5882,17 +5882,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/GIEST66547.2025.11387636</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/GIEST66547.2025.11387636</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5939,17 +5939,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IOT-SIU65919.2025.11402683</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IOT-SIU65919.2025.11402683</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -5996,17 +5996,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/GITCON65266.2025.11379715</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/GITCON65266.2025.11379715</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6053,17 +6053,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/GITCON65266.2025.11376984</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/GITCON65266.2025.11376984</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6110,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/AECE67531.2025.11386640</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/AECE67531.2025.11386640</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6167,17 +6167,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/GITCON65266.2025.11376870</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/GITCON65266.2025.11376870</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -6281,17 +6281,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/GITCON65266.2025.11378263</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/GITCON65266.2025.11378263</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -6395,17 +6395,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/GITCON65266.2025.11377308</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/GITCON65266.2025.11377308</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICECA66444.2025.11383197</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICECA66444.2025.11383197</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.26782/jmcms.2026.05.00002</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.26782/jmcms.2026.05.00002</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6794,17 +6794,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IATMSI68868.2026.11466081</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IATMSI68868.2026.11466081</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6851,17 +6851,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IATMSI68868.2026.11465940</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IATMSI68868.2026.11465940</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6908,17 +6908,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IATMSI68868.2026.11465912</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IATMSI68868.2026.11465912</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -6965,17 +6965,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IETACS68750.2025.11385623</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IETACS68750.2025.11385623</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7022,17 +7022,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICETEG66194.2025.11473233</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICETEG66194.2025.11473233</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7079,17 +7079,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/UPWIECON67212.2025.11390528</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/UPWIECON67212.2025.11390528</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7136,17 +7136,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/InCoWoCo68239.2025.11407118</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/InCoWoCo68239.2025.11407118</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7193,17 +7193,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICOIICS67115.2025.11390169</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICOIICS67115.2025.11390169</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7250,17 +7250,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICOSEC67334.2025.11459566</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICOSEC67334.2025.11459566</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7307,17 +7307,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1016/j.mtcomm.2026.115484</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1016/j.mtcomm.2026.115484</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7364,17 +7364,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1016/j.fraope.2026.100634</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1016/j.fraope.2026.100634</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7421,17 +7421,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1016/j.fraope.2026.100623</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1016/j.fraope.2026.100623</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7535,17 +7535,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ESCI68015.2026.11493313</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ESCI68015.2026.11493313</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7592,17 +7592,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1016/j.rio.2026.101059</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1016/j.rio.2026.101059</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7649,17 +7649,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/MPCON69668.2026.11508621</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/MPCON69668.2026.11508621</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7763,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CIPHER70417.2026.11523934</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CIPHER70417.2026.11523934</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -7877,17 +7877,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/CIPHER70417.2026.11524009</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/CIPHER70417.2026.11524009</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -7934,17 +7934,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IITCEE67948.2026.11394592</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IITCEE67948.2026.11394592</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -8048,17 +8048,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/ICITIIT68860.2026.11499567</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/ICITIIT68860.2026.11499567</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verified (High)</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8162,17 +8162,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IETACS68750.2025.11385512</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IETACS68750.2025.11385512</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8219,17 +8219,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IETACS68750.2025.11385781</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IETACS68750.2025.11385781</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8276,17 +8276,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/AIMLCPS68702.2026.11542403</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/AIMLCPS68702.2026.11542403</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8333,17 +8333,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/AIMLCPS68702.2026.11542368</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/AIMLCPS68702.2026.11542368</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8390,17 +8390,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/AIMLCPS68702.2026.11542453</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/AIMLCPS68702.2026.11542453</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">No DOI / link</t>
         </is>
       </c>
     </row>
@@ -8561,17 +8561,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IC-EETA66496.2025.11547982</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IC-EETA66496.2025.11547982</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
@@ -8618,17 +8618,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">https://doi.org/10.1109/IC-EETA66496.2025.11548424</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">10.1109/IC-EETA66496.2025.11548424</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT FOUND - verify manually</t>
+          <t xml:space="preserve">DOI provided</t>
         </is>
       </c>
     </row>
